--- a/flat_template.xlsx
+++ b/flat_template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
   <si>
     <t>*Action</t>
   </si>
@@ -24,6 +24,9 @@
   </si>
   <si>
     <t>*Category</t>
+  </si>
+  <si>
+    <t>Description</t>
   </si>
   <si>
     <t>*Title</t>
@@ -439,37 +442,38 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="18" max="18" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="23" max="23" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="26.993" bestFit="true" customWidth="true" style="0"/>
     <col min="25" max="25" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="26" max="26" width="22.28" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -544,6 +548,9 @@
       </c>
       <c r="Y1" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/flat_template.xlsx
+++ b/flat_template.xlsx
@@ -20,76 +20,76 @@
     <t>*Action</t>
   </si>
   <si>
+    <t>*Category</t>
+  </si>
+  <si>
+    <t>*Title</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>*ConditionID</t>
+  </si>
+  <si>
+    <t>PicURL</t>
+  </si>
+  <si>
+    <t>*Quantity</t>
+  </si>
+  <si>
+    <t>*Format</t>
+  </si>
+  <si>
+    <t>*StartPrice</t>
+  </si>
+  <si>
+    <t>*Duration</t>
+  </si>
+  <si>
+    <t>*Location</t>
+  </si>
+  <si>
+    <t>ShippingProfileName</t>
+  </si>
+  <si>
+    <t>ReturnProfileName</t>
+  </si>
+  <si>
+    <t>PaymentProfileName</t>
+  </si>
+  <si>
+    <t>C:Marke</t>
+  </si>
+  <si>
+    <t>C:Produktart</t>
+  </si>
+  <si>
     <t>Custom label (SKU)</t>
   </si>
   <si>
-    <t>*Category</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>*Title</t>
-  </si>
-  <si>
-    <t>*ConditionID</t>
-  </si>
-  <si>
     <t>ConditionDescription</t>
   </si>
   <si>
-    <t>*StartPrice</t>
-  </si>
-  <si>
-    <t>*Quantity</t>
-  </si>
-  <si>
-    <t>*Format</t>
-  </si>
-  <si>
-    <t>*Duration</t>
-  </si>
-  <si>
-    <t>*Location</t>
-  </si>
-  <si>
-    <t>ShippingProfileName</t>
-  </si>
-  <si>
-    <t>ReturnProfileName</t>
-  </si>
-  <si>
-    <t>PaymentProfileName</t>
-  </si>
-  <si>
-    <t>PicURL</t>
-  </si>
-  <si>
-    <t>C:Marke</t>
+    <t>C:Herstellernummer</t>
+  </si>
+  <si>
+    <t>C:Produkt</t>
+  </si>
+  <si>
+    <t>C:Modellkompatibilität</t>
+  </si>
+  <si>
+    <t>C:Farbe</t>
   </si>
   <si>
     <t>C:Hersteller</t>
   </si>
   <si>
-    <t>C:Produktart</t>
-  </si>
-  <si>
-    <t>C:Produkt</t>
-  </si>
-  <si>
-    <t>C:Farbe</t>
-  </si>
-  <si>
     <t>C:Material</t>
   </si>
   <si>
     <t>C:Markenkompatibilität</t>
-  </si>
-  <si>
-    <t>C:Modellkompatibilität</t>
-  </si>
-  <si>
-    <t>C:Herstellernummer</t>
   </si>
   <si>
     <t>C:Installationsart</t>
@@ -446,30 +446,30 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="20" max="20" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="26.993" bestFit="true" customWidth="true" style="0"/>
     <col min="26" max="26" width="22.28" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
